--- a/Employee_Reports_wi52/Sathis Gunawardhana Dikella Kandha Yakdhehirallage Q0572.xlsx
+++ b/Employee_Reports_wi52/Sathis Gunawardhana Dikella Kandha Yakdhehirallage Q0572.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1304,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1353,11 +1353,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1402,11 +1402,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1451,11 +1451,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1501,11 +1501,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1550,11 +1550,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1599,11 +1599,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1648,11 +1648,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1697,11 +1697,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1746,11 +1746,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1795,11 +1795,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1844,11 +1844,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1893,11 +1893,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1930,11 +1930,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1967,11 +1967,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2004,11 +2004,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2053,11 +2053,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2102,11 +2102,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2151,11 +2151,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2179,20 +2179,20 @@
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2025</t>
+          <t>25-Aug-2026</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2027</t>
+          <t>24-Aug-2028</t>
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>315</v>
+        <v>727</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7900</v>
+        <v>7892</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7900</v>
+        <v>7892</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7944</v>
+        <v>7936</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7944</v>
+        <v>7936</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7944</v>
+        <v>7936</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7944</v>
+        <v>7936</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7944</v>
+        <v>7936</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7944</v>
+        <v>7936</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
